--- a/master.xlsx
+++ b/master.xlsx
@@ -16,7 +16,8 @@
     <sheet name="Pending Orders" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Settings" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Notes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="_MarketCache" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Manual Data" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="_MarketCache" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -623,7 +624,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-01 07:58 UTC</t>
+          <t>2026-08-02 09:09 UTC</t>
         </is>
       </c>
     </row>
@@ -640,6 +641,96 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SHB-A.ST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>trailing_pe</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>user, Avanza app</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>P/E not available from free automated sources for Swedish tickers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -710,7 +801,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -731,7 +822,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>144.1499938964844</v>
+        <v>145.6499938964844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -740,20 +831,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>144.1499938964844</v>
+        <v>145.6499938964844</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OK (price only)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>yahoo_chart_v8 (fallback — quoteSummary/yfinance unavailable)</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -764,7 +850,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>401.7999877929688</v>
+        <v>404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -773,20 +859,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>401.7999877929688</v>
+        <v>404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>OK (price only)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>yahoo_chart_v8 (fallback — quoteSummary/yfinance unavailable)</t>
         </is>
       </c>
     </row>
@@ -838,7 +919,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -896,7 +977,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1619.14</v>
+        <v>1615.68</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -905,7 +986,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -935,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -965,7 +1046,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-01T07:58:06.876265+00:00</t>
+          <t>2026-08-02T09:08:57.430432+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">

--- a/master.xlsx
+++ b/master.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-02 09:09 UTC</t>
+          <t>2026-08-02 09:52 UTC</t>
         </is>
       </c>
     </row>
@@ -801,8 +801,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
-        </is>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -831,11 +834,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>145.6499938964844</v>
+        <v>145.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,7 +922,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -977,7 +980,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1615.68</v>
+        <v>1620.75</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -986,8 +989,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
-        </is>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>17898.2664</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1016,8 +1022,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
-        </is>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>9.6998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1046,8 +1055,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-02T09:08:57.430432+00:00</t>
-        </is>
+          <t>2026-08-02T09:51:47.510979+00:00</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>11.0432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-02 09:52 UTC</t>
+          <t>2026-08-02 10:03 UTC</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1620.75</v>
+        <v>1620.59</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -989,11 +989,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17898.2664</v>
+        <v>17896.4995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-02T09:51:47.510979+00:00</t>
+          <t>2026-08-02T10:03:21.567440+00:00</t>
         </is>
       </c>
       <c r="E12" t="n">

--- a/master.xlsx
+++ b/master.xlsx
@@ -4955,7 +4955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5702,6 +5702,28 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sweep-2026-08-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>First sweep under consolidated single-report format (reports/2026-08-02-sweep.md), nothing to reconcile against. Headline items: (1) Two Pending Orders awaiting execution confirmation - Visa 7,500 SEK and Schneider Electric (SU.PA) 5,000 SEK, both committed 2026-07-29. (2) Settings sheet contribution_routing_default still says 100% to Secure tier, conflicts with current Medium-tier priority given 90.1%-vs-60% Secure drift - needs update. (3) Open decision: whether to write SHB-A.ST/INVE-A.ST theses now on insider-buying signal (Boman/Lundberg SHB-A.ST, Cederholm INVE-A.ST) vs wait for confirmed fundamentals (INVE-A.ST CIK fetch broken, SHB-A.ST PE is manual override); both at/near 52w highs, no written thesis exists. (4) Open decision: Swedbank AF fund cost basis unknown - request from Swedbank statement vs leave as legacy holding.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master.xlsx
+++ b/master.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-02 10:03 UTC</t>
+          <t>2026-08-02 17:20 UTC</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1620.59</v>
+        <v>1616.08</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -989,11 +989,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17896.4995</v>
+        <v>17846.6947</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-02T10:03:21.567440+00:00</t>
+          <t>2026-08-02T17:20:00.012726+00:00</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1083,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1708,22 +1708,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CASH_SEK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Swedbank fund</t>
+          <t>SEB fund proceeds - fully transferred to Avanza ISK 2026-07-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>swedbank-fund</t>
+          <t>seb-fund</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Swedbank</t>
+          <t>SEB</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1733,149 +1733,152 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>LIKELY UNLISTED FUND (inferred 2026-07-31, NOT explicitly confirmed by user - flag if this differs): probably a Swedbank Robur-style fund on Swedbank's own platform, same structural situation as Avanza Auto 3/Avanza Global. Treated as probably-permanent pending user confirmation, not re-flagged as an urgent open item each sweep.</t>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Legacy childhood savings - no active thesis. Decision needed: keep, or realize small gain and move into ISK.…see Investment Thesis sheet</t>
+          <t>Not an investment. Full 17,382.43 SEK transferred to Avanza ISK 2026-07-20 (see avanza-isk cash holding). Realized gain still unknown - open question 4 not closed by this transfer, only the practical …see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CASH_SEK</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SEB fund proceeds - fully transferred to Avanza ISK 2026-07-20</t>
+          <t>ETH (self-custody wallet)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>seb-fund</t>
+          <t>eth-wallet</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEB</t>
+          <t>personal wallet</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>SELF_CUSTODY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>spot_crypto</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>crypto</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Not an investment. Full 17,382.43 SEK transferred to Avanza ISK 2026-07-20 (see avanza-isk cash holding). Realized gain still unknown - open question 4 not closed by this transfer, only the practical …see Investment Thesis sheet</t>
+          <t>TBD…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>CASH_USD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETH (self-custody wallet)</t>
+          <t>PayPal USD balance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eth-wallet</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>personal wallet</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SELF_CUSTODY</t>
+          <t>PAYPAL_BALANCE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>spot_crypto</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>crypto</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1177.49</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>TBD…see Investment Thesis sheet</t>
+          <t>Not an investment - idle payment-platform balance from incoming payments. Sits outside any wrapper, earns nothing, and is exposed to PayPal's conversion spread on any USD-&gt;SEK move. Needs a routing de…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CASH_USD</t>
+          <t>CASH_EUR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PayPal USD balance</t>
+          <t>PayPal EUR balance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1910,68 +1913,13 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1177.49</v>
+        <v>266.88</v>
       </c>
       <c r="P14" t="inlineStr">
-        <is>
-          <t>Not an investment - idle payment-platform balance from incoming payments. Sits outside any wrapper, earns nothing, and is exposed to PayPal's conversion spread on any USD-&gt;SEK move. Needs a routing de…see Investment Thesis sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CASH_EUR</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PayPal EUR balance</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>paypal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PAYPAL_BALANCE</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>266.88</v>
-      </c>
-      <c r="P15" t="inlineStr">
         <is>
           <t>Not an investment - idle payment-platform balance. Recurring EUR inflow (~750-1000 EUR / ~2mo) lands here - same routing decision as the USD balance applies, and matters more given the recurring caden…see Investment Thesis sheet</t>
         </is>
@@ -4174,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4352,7 +4300,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedbank fund</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4367,14 +4315,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Legacy childhood savings - no active thesis. Decision needed: keep, or realize small gain and move into ISK.</t>
+          <t>TBD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>SU.PA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4384,19 +4332,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>see thesis text</t>
+          <t>candidate — not held</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Western grid-buildout and energy-transition spending; data-center power demand.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Electrification + data-center power demand (the 'shovel' of the AI build-out) + energy-efficiency, all policy-funded. Quality compounder with pricing power; genuinely sustainability-aligned (its product IS efficiency, not a bolt-on label). Fits the user's Europe + sustainability + growth preference. Highest-conviction of this set.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SU.PA</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4416,19 +4374,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Western grid-buildout and energy-transition spending; data-center power demand.</t>
+          <t>US CHIPS Act + EU Chips Act reshoring subsidies drive fab build-out.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Electrification + data-center power demand (the 'shovel' of the AI build-out) + energy-efficiency, all policy-funded. Quality compounder with pricing power; genuinely sustainability-aligned (its product IS efficiency, not a bolt-on label). Fits the user's Europe + sustainability + growth preference. Highest-conviction of this set.</t>
+          <t>Effective monopoly on EUV lithography — no advanced chip exists without its machines. Wide moat, high margins, secular semiconductor demand.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4443,24 +4401,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>US CHIPS Act + EU Chips Act reshoring subsidies drive fab build-out.</t>
+          <t>EV adoption + electrification policy.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Effective monopoly on EUV lithography — no advanced chip exists without its machines. Wide moat, high margins, secular semiconductor demand.</t>
+          <t>European power-semiconductor leader levered to EV and industrial electrification — sustainability-adjacent growth.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>IBE.MC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4475,24 +4433,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EV adoption + electrification policy.</t>
+          <t>Renewable-energy subsidies and grid investment.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>European power-semiconductor leader levered to EV and industrial electrification — sustainability-adjacent growth.</t>
+          <t>Renewables-heavy regulated utility — a real sustainability holding and a steadier ballast within the medium tier.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IBE.MC</t>
+          <t>NOVO-B.CO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4507,24 +4465,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Renewable-energy subsidies and grid investment.</t>
+          <t>Drug-pricing politics run AGAINST this one (US pricing pressure) — a headwind, flagged honestly.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Renewables-heavy regulated utility — a real sustainability holding and a steadier ballast within the medium tier.</t>
+          <t>GLP-1 (obesity/diabetes) structural demand; dominant franchise, high margins.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOVO-B.CO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4544,42 +4502,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Drug-pricing politics run AGAINST this one (US pricing pressure) — a headwind, flagged honestly.</t>
+          <t>Reshoring subsidies (CHIPS Act) fund its US fabs.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>GLP-1 (obesity/diabetes) structural demand; dominant franchise, high margins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>candidate — not held</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Reshoring subsidies (CHIPS Act) fund its US fabs.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>The foundry essentially all advanced chips depend on; scale and process-node lead form a deep moat.</t>
         </is>
@@ -5055,12 +4981,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Swedbank fund: current gain vs cost basis (feeds move-to-ISK calculation).</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>User confirmed 2026-08-02: no Swedbank fund ever existed. This was a migration-time inference error - the real legacy holding was the SEB funds (SEB Europafond, SEB Nordenfond A, SEB Obligationsfond Flexibel A, SEB Sverigefond, SEB Global Focus C USD, SEB Emerging Markets C USD Lux, SEB Emerging Marketsfond), all sold 2026-07-08/09/10 and fully transferred to Avanza ISK 2026-07-20 (see Transactions sheet, account_id seb-fund, and the CASH_SEK row SEB fund proceeds...). Phantom Portfolio/Investment Thesis rows for Swedbank fund deleted.</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5128,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>avanza-isk's non-cash holdings re-itemization - PARTIALLY RESOLVED 2026-07-31: SHB-A.ST and INVE-A.ST now fetch real, fresh prices again (fetch_equities() fixed, see IMPROVEMENTS #17) - price 146.15 / 406.40 SEK respectively as of 2026-07-31, still no fundamentals (no free source for non-US names). Avanza Auto 3 and the two unlisted funds (Avanza Global, Swedbank fund) will NEVER get exchange-fetched prices - see their no_ticker_reason fields, this is structural not pending. COIN-XBT.ST remains unresolved (ticker doesn't match Yahoo under any tried variant) - see open question 13/19 below, may be moot if the Valour Bitcoin Zero switch happens.</t>
+          <t>avanza-isk's non-cash holdings re-itemization - PARTIALLY RESOLVED 2026-07-31: SHB-A.ST and INVE-A.ST now fetch real, fresh prices again (fetch_equities() fixed, see IMPROVEMENTS #17) - price 146.15 / 406.40 SEK respectively as of 2026-07-31, still no fundamentals (no free source for non-US names). Avanza Auto 3 and Avanza Global will NEVER get exchange-fetched prices - see their no_ticker_reason fields, this is structural not pending. (Correction 2026-08-02: a third TBD unlisted-fund row, Swedbank fund, previously listed here was a migration-time error and has been deleted - see Notes id 3.) COIN-XBT.ST remains unresolved (ticker does not match Yahoo under any tried variant) - see open question 13/19 below, may be moot if the Valour Bitcoin Zero switch happens.</t>
         </is>
       </c>
     </row>

--- a/master.xlsx
+++ b/master.xlsx
@@ -4522,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Data-confirmed quality anchor from the stacked funnel (rank_candidates.py): ~50% net margins, low realized risk (data_risk_score 25), payments-duopoly moat. CAUTION (root-caused and FIXED 2026-07-29, see IMPROVEMENTS #13): the ranker's PE of 8.7 was WRONG - SEC's share-count feed for Visa hadn't updated since 2010 (Visa moved to per-class reporting the free API can't aggregate), so a 16-year-stale count was silently used as current. Fixed with a staleness guard (fetch_fundamentals.py:_shares) that now correctly returns 'no data' for Visa's share count instead of a wrong number - PE/EPS are null post-fix, not a false 8.7. Real-world PE is in the 30-35 range (premium, not cheap) - buy the quality/moat thesis, not a mispriced 'cheap' signal.</t>
+          <t>Data-confirmed quality anchor from the stacked funnel (rank_candidates.py): ~50% net margins, low realized risk (data_risk_score 25), payments-duopoly moat. CAUTION (root-caused and FIXED 2026-07-29): the ranker's PE of 8.7 was WRONG - SEC's share-count feed hadn't updated since 2010, fixed with a staleness guard - PE/EPS are null post-fix, not a false 8.7. Real-world PE is in the 30-35 range (premium, not cheap) per background knowledge, not live-fetched - buy the quality/moat thesis. REVISED 2026-08-02: resized from 7,500 to 6,000 SEK as part of a coordinated 5-name, 24,000 SEK allocation (Visa/Atlas Copco/healthcare pick/Schneider/Volvo), funded from idle Avanza ISK cash, overriding the original single-name commitment.</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4653,7 +4653,87 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Thesis-driven pick (data/thesis_candidates.json) - electrification, data-center power demand, energy-transition policy tailwinds; sustainability-aligned. Momentum-only on free data (no US-style fundamentals available for European filers), so this is a thesis position sized deliberately small given it isn't fundamentally confirmed.</t>
+          <t>Thesis-driven pick (data/thesis_candidates.json) - electrification, data-center power demand, energy-transition policy tailwinds; sustainability-aligned. Momentum-only on free data (no US-style fundamentals available for European filers), so this is a thesis position sized deliberately small given it isn't fundamentally confirmed. REVISED 2026-08-02: resized from 5,000 to 4,800 SEK as part of a coordinated 5-name, 24,000 SEK allocation, funded from idle Avanza ISK cash, overriding the original single-name commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ATCO-B.ST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Atlas Copco B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>avanza-isk</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>user-committed, execution not yet confirmed</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Part of the user's coordinated 5-name, 24,000 SEK allocation (2026-08-02), funded from idle Avanza ISK cash. No free fundamentals source (non-US filer, structural gap). Insider signal from Finansinspektionen is MIXED-TO-CAUTIONARY, not supportive: mostly option exercises plus two executives (Henrik Elmin, Sara Hagg Liljedal) selling (Avyttring) at 197.5-199.5 SEK, near/above the fetched price of 175.85 SEK (B shares). One small real buy (Kenneth Lagerborg, 7,000 sh, 2026-06-09, 161.57 SEK). B shares recommended over A (201.10 SEK) - same economic claim, voting-rights premium irrelevant at retail scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VOLV-B.ST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Volvo AB B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>avanza-isk</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>user-committed, execution not yet confirmed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Part of the user's coordinated 5-name, 24,000 SEK allocation (2026-08-02), funded from idle Avanza ISK cash. No free fundamentals source (non-US filer, structural gap). Insider signal from Finansinspektionen is genuinely strong: board member Helena Stjernholm bought ~1.3M shares total at ~360 SEK on 2026-07-27, matching AB Volvo's actual fetched price (364.30 SEK) - real, recent, sizeable conviction buying, the best-evidenced leg of the five. NOTE: the same issuer search also returned CEO/CFO purchases at ~19 SEK, almost certainly a DIFFERENT listed entity (likely Volvo Car Group, separately listed) - excluded from this signal, not counted as supporting evidence.</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5660,6 +5740,28 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Coordinated 5-name, 24,000 SEK Avanza ISK cash deployment (2026-08-02): Visa (V, 6,000 SEK), Atlas Copco (ATCO-B.ST, 6,000 SEK), Schneider Electric (SU.PA, 4,800 SEK), Volvo AB (VOLV-B.ST, 2,400 SEK) all recorded as Pending Orders. Healthcare pick (4,800 SEK, 20%) still undecided between Stryker (SYK, real P/E ~38.5x, margin 12.9%, revenue growth 11.2%, ROE 27.7%) and Abbott (ABT, real P/E ~28.2x, margin 14.7%, revenue growth 5.7%, ROE 12.5%) - both verified via SEC data; Novo Nordisk considered but has zero fundamentals/insider data available in this system (Danish issuer, outside every free source used) so it would be bought on reputation, not verified data. Resolve before executing the healthcare leg.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master.xlsx
+++ b/master.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Notes" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Manual Data" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="_MarketCache" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="_ValueHistory" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +68,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +79,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F6E63"/>
         <bgColor rgb="001F6E63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBF7"/>
+        <bgColor rgb="00DCEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DCF7"/>
+        <bgColor rgb="00E6DCF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,10 +135,57 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DCEBF7"/>
+          <bgColor rgb="00DCEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
+          <bgColor rgb="00E2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
+          <bgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
+          <bgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E6DCF7"/>
+          <bgColor rgb="00E6DCF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -178,6 +256,151 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Total portfolio value (SEK)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'_ValueHistory'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'_ValueHistory'!$A$2:$A$200</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'_ValueHistory'!$B$2:$B$200</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>SEK</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -469,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -505,12 +728,12 @@
         </is>
       </c>
       <c r="B5">
-        <f>SUMPRODUCT((Portfolio!J2:J1000)*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))</f>
+        <f>SUMPRODUCT((Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIF(Portfolio!A2:A1000,"TBD",Portfolio!L2:L1000)</f>
         <v/>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sum of each holding's quantity x current price, from _MarketCache</t>
+          <t>Sum of each holding's quantity x current price (from _MarketCache), plus cost basis for unlisted funds (never get a live price)</t>
         </is>
       </c>
     </row>
@@ -545,7 +768,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>SUMPRODUCT((Portfolio!H2:H1000="secure")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))/SUMPRODUCT((Portfolio!J2:J1000)*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),1))</f>
+        <f>(SUMPRODUCT((Portfolio!H2:H1000="secure")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!H2:H1000,"secure",Portfolio!A2:A1000,"TBD"))/$B$5</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr">
@@ -561,7 +784,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>SUMPRODUCT((Portfolio!H2:H1000="medium")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))/SUMPRODUCT((Portfolio!J2:J1000)*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),1))</f>
+        <f>(SUMPRODUCT((Portfolio!H2:H1000="medium")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!H2:H1000,"medium",Portfolio!A2:A1000,"TBD"))/$B$5</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr">
@@ -577,7 +800,7 @@
         </is>
       </c>
       <c r="B11">
-        <f>SUMPRODUCT((Portfolio!H2:H1000="high")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))/SUMPRODUCT((Portfolio!J2:J1000)*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),1))</f>
+        <f>(SUMPRODUCT((Portfolio!H2:H1000="high")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!H2:H1000,"high",Portfolio!A2:A1000,"TBD"))/$B$5</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr">
@@ -600,12 +823,12 @@
         </is>
       </c>
       <c r="B14">
-        <f>SUMPRODUCT(Portfolio!M2:M1000/100*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))</f>
+        <f>SUMPRODUCT((Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!M2:M1000/100*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMPRODUCT((Portfolio!A2:A1000="TBD")*Portfolio!M2:M1000/100*Portfolio!L2:L1000)</f>
         <v/>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Sum of annual_fee_pct x market value per holding</t>
+          <t>Sum of annual_fee_pct x market value per holding (cost basis for unlisted funds)</t>
         </is>
       </c>
     </row>
@@ -624,12 +847,125 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-02 17:20 UTC</t>
+          <t>(set by run.py sync)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BY TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Value (SEK)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Stocks</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>SUMPRODUCT((Portfolio!F2:F1000="stock")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!F2:F1000,"stock",Portfolio!A2:A1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(Portfolio!F2:F1000,"stock")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Funds</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>SUMPRODUCT((Portfolio!F2:F1000="fund")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!F2:F1000,"fund",Portfolio!A2:A1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>COUNTIF(Portfolio!F2:F1000,"fund")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Certificates</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>SUMPRODUCT((Portfolio!F2:F1000="certificate")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!F2:F1000,"certificate",Portfolio!A2:A1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>COUNTIF(Portfolio!F2:F1000,"certificate")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>SUMPRODUCT((Portfolio!F2:F1000="cash")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!F2:F1000,"cash",Portfolio!A2:A1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>COUNTIF(Portfolio!F2:F1000,"cash")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>SUMPRODUCT((Portfolio!F2:F1000="spot_crypto")*(Portfolio!A2:A1000&lt;&gt;"TBD")*Portfolio!J2:J1000*IFERROR(VLOOKUP(Portfolio!A2:A1000,_MarketCache!A:E,5,0),0))+SUMIFS(Portfolio!L2:L1000,Portfolio!F2:F1000,"spot_crypto",Portfolio!A2:A1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>COUNTIF(Portfolio!F2:F1000,"spot_crypto")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PERFORMANCE OVER TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>See chart below — logged automatically by `run.py fetch` into the hidden _ValueHistory sheet each time it runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Add new KPIs below this line — this sheet is designed to grow.</t>
         </is>
@@ -637,6 +973,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -736,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -801,7 +1138,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -821,91 +1158,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SHB-A.ST</t>
+          <t>CASH_USD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>145.6499938964844</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>145.65</v>
+        <v>9.6998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cash</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INVE-A.ST</t>
+          <t>CASH_EUR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>404</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>404</v>
+        <v>11.0432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OK (price only)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cash</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TBD-Avanza Auto 3 (fund)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>9800.299999999999</v>
+          <t>COIN-XBT.ST</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>N/A (permanent)</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>unlisted_fund</t>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TBD-Tundra Sustainable Frontier Fund A SEK</t>
+          <t>TBD-Avanza Auto 3 (fund)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1000</v>
+        <v>9800.299999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A (permanent)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -917,22 +1266,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COIN-XBT.ST</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
-        </is>
+          <t>TBD-Tundra Sustainable Frontier Fund A SEK</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>unlisted_fund</t>
         </is>
       </c>
     </row>
@@ -942,6 +1294,11 @@
           <t>TBD-Avanza Global (fund)</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
       <c r="E8" t="n">
         <v>119999</v>
       </c>
@@ -959,116 +1316,200 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TBD-Swedbank fund</t>
-        </is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1619.61</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17885.6772</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>N/A (permanent)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>unlisted_fund</t>
+          <t>coingecko</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>SHB-A.ST</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1616.08</v>
+        <v>145.6499938964844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17846.6947</v>
+        <v>145.65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>coingecko</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CASH_USD</t>
+          <t>INVE-A.ST</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
+          <t>2026-08-02T18:13:39.316480+00:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.6998</v>
+        <v>404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CASH_EUR</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-08-02T17:20:00.012726+00:00</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>11.0432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>cash</t>
+          <t>OK (price only)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>total_value_sek</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>192500</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>third automated sweep - holdings unchanged since 2026-07-06 second sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>226935</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>same-day reconciliation, NOT organic growth: PayPal balance counted for the first time (14321 SEK), SEB final settlement confirmed exact (17382 vs prior ~18k estimate), Avanza ISK itemized exactly (36120 vs 36000 approx), HB now confirmed-sold cash (136612 vs 134894 pre-sale estimate). Do not treat the ~34.4k jump from the prior row as investment gain - it is data completeness. See SESSION_LOG.md 2026-07-13 entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>226905</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>weekly automated sweep, holdings/accounts unchanged from 07-13 (HB/SEB cash still untransferred, no new contributions logged in portfolio.json). ~30 SEK variance vs the 226935 prior row is FX/price movement (fresh ETH price this sweep), not a data-completeness event. Equities (SHB-A.ST, INVE-A.ST, COIN-XBT.ST) priced at last-known 07-13 values - org egress policy blocked a fresh equities fetch this sweep, see SESSION_LOG.md 2026-07-20 entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>227703</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>user-triggered follow-up sweep, NOT organic growth: found money (+17 SEK at hb-main), new hb-checking account counted for the first time (611 SEK), Avanza ISK confirmed live by user (181254 vs computed 181114.26). No new contributions logged in portfolio.json. Equities still priced at stale 07-13 values - fetch blocked 3rd consecutive sweep. See SESSION_LOG.md 2026-07-22 entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>183361.44</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>auto-logged by run.py fetch</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1750,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SHB-A.ST</t>
+          <t>CASH_SEK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handelsbanken A (stock)</t>
+          <t>Avanza ISK available cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1334,124 +1775,152 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SEK</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>26399.86</v>
       </c>
       <c r="K4" t="n">
         <v>129.25</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 5.58%, P/E 11.95. Next report 2026-07-15 (delarsrapport) - unrelated to the pending HB fondkonto…see Investment Thesis sheet</t>
+          <t>Not an investment - uninvested cash. RECONCILED 2026-07-29: prior 144,864 SEK (confirmed 2026-07-22) minus the 119,999 SEK Avanza Global purchase plus the 1,534.86 SEK Tundra sale proceeds = 26,399.86…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INVE-A.ST</t>
+          <t>CASH_SEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Investor A (stock)</t>
+          <t>SEB fund proceeds - fully transferred to Avanza ISK 2026-07-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>avanza-isk</t>
+          <t>seb-fund</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avanza</t>
+          <t>SEB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ISK</t>
+          <t>AF</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SEK</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>290.22</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 1.45%, P/E 6.22. Next report 2026-07-16 (delarsrapport).…see Investment Thesis sheet</t>
+          <t>Not an investment. Full 17,382.43 SEK transferred to Avanza ISK 2026-07-20 (see avanza-isk cash holding). Realized gain still unknown - open question 4 not closed by this transfer, only the practical …see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CASH_USD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Avanza Auto 3 (fund)</t>
+          <t>PayPal USD balance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>avanza-isk</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avanza</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ISK</t>
+          <t>PAYPAL_BALANCE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>secure</t>
-        </is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1177.49</v>
       </c>
       <c r="L6" t="n">
         <v>9800.299999999999</v>
@@ -1466,53 +1935,58 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONFIRMED from factsheet 2026-07-22: multi-asset fund, ~60% equity exposure (40-70% range) blended with bonds/alternatives, 0.39% total annual fee (0.35% management + ~0.04% transaction), recommended …see Investment Thesis sheet</t>
+          <t>Not an investment - idle payment-platform balance from incoming payments. Sits outside any wrapper, earns nothing, and is exposed to PayPal's conversion spread on any USD-&gt;SEK move. Needs a routing de…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CASH_EUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tundra Sustainable Frontier Fund A SEK</t>
+          <t>PayPal EUR balance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>avanza-isk</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avanza</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ISK</t>
+          <t>PAYPAL_BALANCE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EUR</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="L7" t="n">
         <v>1000</v>
@@ -1522,7 +1996,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SOLD 2026-07-29 (user-confirmed EXECUTED, exact trade date not specified - sits within the 2026-07-22 to 2026-07-29 window): sale settled for 1,534.86 SEK proceeds (vs. the 1,563 SEK stale 2026-07-13 …see Investment Thesis sheet</t>
+          <t>Not an investment - idle payment-platform balance. Recurring EUR inflow (~750-1000 EUR / ~2mo) lands here - same routing decision as the USD balance applies, and matters more given the recurring caden…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
@@ -1590,7 +2064,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Avanza Global (fund)</t>
+          <t>Avanza Auto 3 (fund)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1615,7 +2089,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1624,10 +2098,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>119999</v>
+        <v>9800.299999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1636,24 +2110,24 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>UNLISTED FUND (user-confirmed 2026-07-31) - Avanza Global exists only on Avanza's own fund platform, not on a public exchange. No ticker/ISIN will ever resolve for it via Yahoo/SEC or any exchange-based fetch. This is PERMANENT, not a data gap awaiting a fix - do not keep re-flagging it as an open item each sweep.</t>
+          <t>UNLISTED FUND (user-confirmed 2026-07-31) - Avanza Auto 3 exists only on Avanza's own fund platform, not on a public exchange. No ticker/ISIN will ever resolve for it via Yahoo/SEC or any exchange-based fetch. This is PERMANENT, not a data gap awaiting a fix - do not keep re-flagging it as an open item each sweep.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SETTLED 2026-07-29 (user-confirmed EXECUTED - this was previously recommended as the secure-tier deployment core but had NOT been logged as bought; user flagged the logging gap 2026-07-29). Global equ…see Investment Thesis sheet</t>
+          <t>CONFIRMED from factsheet 2026-07-22: multi-asset fund, ~60% equity exposure (40-70% range) blended with bonds/alternatives, 0.39% total annual fee (0.35% management + ~0.04% transaction), recommended …see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASH_SEK</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Avanza ISK available cash</t>
+          <t>Tundra Sustainable Frontier Fund A SEK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +2147,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1692,7 +2166,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26399.86</v>
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1701,49 +2181,49 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Not an investment - uninvested cash. RECONCILED 2026-07-29: prior 144,864 SEK (confirmed 2026-07-22) minus the 119,999 SEK Avanza Global purchase plus the 1,534.86 SEK Tundra sale proceeds = 26,399.86…see Investment Thesis sheet</t>
+          <t>SOLD 2026-07-29 (user-confirmed EXECUTED, exact trade date not specified - sits within the 2026-07-22 to 2026-07-29 window): sale settled for 1,534.86 SEK proceeds (vs. the 1,563 SEK stale 2026-07-13 …see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CASH_SEK</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEB fund proceeds - fully transferred to Avanza ISK 2026-07-20</t>
+          <t>Avanza Global (fund)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>seb-fund</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SEB</t>
+          <t>Avanza</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>ISK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>fund</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>secure</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,14 +2234,25 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
+      <c r="L11" t="n">
+        <v>119999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-29 (approximate - user reported the purchase 2026-07-29 as having happened 'a couple of days ago'; exact trade date not yet confirmed)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>UNLISTED FUND (user-confirmed 2026-07-31) - Avanza Global exists only on Avanza's own fund platform, not on a public exchange. No ticker/ISIN will ever resolve for it via Yahoo/SEC or any exchange-based fetch. This is PERMANENT, not a data gap awaiting a fix - do not keep re-flagging it as an open item each sweep.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Not an investment. Full 17,382.43 SEK transferred to Avanza ISK 2026-07-20 (see avanza-isk cash holding). Realized gain still unknown - open question 4 not closed by this transfer, only the practical …see Investment Thesis sheet</t>
+          <t>SETTLED 2026-07-29 (user-confirmed EXECUTED - this was previously recommended as the secure-tier deployment core but had NOT been logged as bought; user flagged the logging gap 2026-07-29). Global equ…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
@@ -1818,42 +2309,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CASH_USD</t>
+          <t>SHB-A.ST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PayPal USD balance</t>
+          <t>Handelsbanken A (stock)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Avanza</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PAYPAL_BALANCE</t>
+          <t>ISK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1862,53 +2353,56 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1177.49</v>
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>129.25</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Not an investment - idle payment-platform balance from incoming payments. Sits outside any wrapper, earns nothing, and is exposed to PayPal's conversion spread on any USD-&gt;SEK move. Needs a routing de…see Investment Thesis sheet</t>
+          <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 5.58%, P/E 11.95. Next report 2026-07-15 (delarsrapport) - unrelated to the pending HB fondkonto…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CASH_EUR</t>
+          <t>INVE-A.ST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PayPal EUR balance</t>
+          <t>Investor A (stock)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Avanza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PAYPAL_BALANCE</t>
+          <t>ISK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1917,15 +2411,35 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>266.88</v>
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>290.22</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Not an investment - idle payment-platform balance. Recurring EUR inflow (~750-1000 EUR / ~2mo) lands here - same routing decision as the USD balance applies, and matters more given the recurring caden…see Investment Thesis sheet</t>
+          <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 1.45%, P/E 6.22. Next report 2026-07-16 (delarsrapport).…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:P1000">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>$F2="stock"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>$F2="fund"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>$F2="certificate"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="3">
+      <formula>$F2="cash"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="4">
+      <formula>$F2="spot_crypto"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tundra Sustainable Frontier Fund A SEK</t>
+          <t>Avanza Global (fund)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>secure</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2169,152 +2169,144 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1000</v>
+        <v>119999</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-29 (approximate - user reported the purchase 2026-07-29 as having happened 'a couple of days ago'; exact trade date not yet confirmed)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>UNLISTED FUND (user-confirmed 2026-07-31) - Avanza Global exists only on Avanza's own fund platform, not on a public exchange. No ticker/ISIN will ever resolve for it via Yahoo/SEC or any exchange-based fetch. This is PERMANENT, not a data gap awaiting a fix - do not keep re-flagging it as an open item each sweep.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SOLD 2026-07-29 (user-confirmed EXECUTED, exact trade date not specified - sits within the 2026-07-22 to 2026-07-29 window): sale settled for 1,534.86 SEK proceeds (vs. the 1,563 SEK stale 2026-07-13 …see Investment Thesis sheet</t>
+          <t>SETTLED 2026-07-29 (user-confirmed EXECUTED - this was previously recommended as the secure-tier deployment core but had NOT been logged as bought; user flagged the logging gap 2026-07-29). Global equ…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Avanza Global (fund)</t>
+          <t>ETH (self-custody wallet)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>avanza-isk</t>
+          <t>eth-wallet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avanza</t>
+          <t>personal wallet</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ISK</t>
+          <t>SELF_CUSTODY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fund</t>
+          <t>spot_crypto</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>crypto</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>secure</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>119999</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-07-29 (approximate - user reported the purchase 2026-07-29 as having happened 'a couple of days ago'; exact trade date not yet confirmed)</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>UNLISTED FUND (user-confirmed 2026-07-31) - Avanza Global exists only on Avanza's own fund platform, not on a public exchange. No ticker/ISIN will ever resolve for it via Yahoo/SEC or any exchange-based fetch. This is PERMANENT, not a data gap awaiting a fix - do not keep re-flagging it as an open item each sweep.</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SETTLED 2026-07-29 (user-confirmed EXECUTED - this was previously recommended as the secure-tier deployment core but had NOT been logged as bought; user flagged the logging gap 2026-07-29). Global equ…see Investment Thesis sheet</t>
+          <t>TBD…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>SHB-A.ST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETH (self-custody wallet)</t>
+          <t>Handelsbanken A (stock)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eth-wallet</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>personal wallet</t>
+          <t>Avanza</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SELF_CUSTODY</t>
+          <t>ISK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>spot_crypto</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>crypto</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>129.25</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>TBD…see Investment Thesis sheet</t>
+          <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 5.58%, P/E 11.95. Next report 2026-07-15 (delarsrapport) - unrelated to the pending HB fondkonto…see Investment Thesis sheet</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHB-A.ST</t>
+          <t>INVE-A.ST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Handelsbanken A (stock)</t>
+          <t>Investor A (stock)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2349,74 +2341,16 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>129.25</v>
+        <v>290.22</v>
       </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 5.58%, P/E 11.95. Next report 2026-07-15 (delarsrapport) - unrelated to the pending HB fondkonto…see Investment Thesis sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>INVE-A.ST</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Investor A (stock)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>avanza-isk</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Avanza</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ISK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>equity</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>290.22</v>
-      </c>
-      <c r="P14" t="inlineStr">
         <is>
           <t>TBD - itemized 2026-07-13 from live Avanza snapshot, no stated reason for holding yet. Direktavkastning 1.45%, P/E 6.22. Next report 2026-07-16 (delarsrapport).…see Investment Thesis sheet</t>
         </is>
@@ -4636,7 +4570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4748,7 +4682,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tundra Sustainable Frontier Fund A SEK</t>
+          <t>COIN-XBT.ST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4763,14 +4697,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SOLD 2026-07-29 (user-confirmed EXECUTED, exact trade date not specified - sits within the 2026-07-22 to 2026-07-29 window): sale settled for 1,534.86 SEK proceeds (vs. the 1,563 SEK stale 2026-07-13 estimate used for planning - real settlement came in ~28 SEK lower). Tax-free inside the ISK (only broker fees applied). Reason: 2.6% total annual fee (6.7x Avanza Auto 3's 0.39%) was unjustifiable fee drag - lever #2. Proceeds folded into the avanza-isk cash holding, which then funded part of the Avanza Global purchase (see that holding). Was open question 14, now fully resolved and executed. History: CONFIRMED from factsheet 2026-07-22 as an actively managed frontier/EM equity fund, &gt;=80% frontier/EM, ESG exclusions, recommended holding period 5 years; cost basis 1,000 SEK, so realized gain ~534.86 SEK, tax-free.</t>
+          <t>SEE ALSO open question 19 (2026-07-31): a candidate fee-drag switch to Valour Bitcoin Zero SEK (0% mgmt fee vs this certificate's 2.5-3.64%) is under evaluation - would preserve full BTC exposure (compatible with the hold decision below), not yet executed, spread/liquidity unverified. HOLD / SOFT-CAP DECISION 2026-07-22 (user-directed, REVERSES the earlier same-day trim): user will NOT sell any bitcoin for now. Total crypto (ETH 12,500 + COIN 16,503.12 = 29,003) stays at ~14.2% of the 203,754 SEK investable base, ABOVE the 10% high-risk-tier cap - user explicitly accepts the cap being breached for now ('if that means raising the crypto/high risk bar, then so be it for now'). Rationale: the active bullish BTC thesis (cycle position, mid-2028 halving) outweighs mechanical cap discipline at this time. SOFT-CAP mechanism instead of a sale: route this deployment and future monthly contributions to the secure/medium tiers so crypto DILUTES back toward 10% over time; revisit an actual trim only if crypto appreciates materially further (e.g. past ~15-16%). No tax event (nothing sold). Certificate-vs-self-custody (open Q13) remains SEPARATE; 'for now' answer is to KEEP the retained BTC in the ISK certificate - tax shelter beats the 2.5% fee at this size/horizon, and the user already holds direct/self-custody crypto via the ETH wallet. --- Original thesis (still held), user's own words: crypto is 'pretty low valued right now,' mid-2028 Bitcoin halving ahead, and there are 'positive buy-in signals now' - this is a cycle-position thesis for BTC exposure generally, not specific to the certificate structure. Separately, user has stated a structural preference for 'real bitcoin instead of certificates' going forward - see open_structural_questions for the certificate-vs-self-custody decision, not yet resolved. Factsheet CONFIRMED 2026-07-22: 2.5% annual management fee, tracks BTC ~1:1 before fees, no capital protection, high volatility/USD currency risk. Early redemption directly with the issuer incurs a 2% exit fee - does NOT apply to an ordinary exchange sale (broker fees apply instead). Live price CONFIRMED 2026-07-22 (user-reported from Avanza): market value 16,503.12 SEK (2,750.52/unit), up 36.39% (+4,403.12 SEK) since purchase (12,100 SEK cost basis for 6 units, consistent with the recorded 2,016.67/unit cost basis). Combined with the ETH wallet (12,500 SEK), total crypto exposure is now ~29,003.12 SEK - above both the 5% glidepath target and the 10% risk-tier cap; sizing decision pending, see open_structural_questions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COIN-XBT.ST</t>
+          <t>Avanza Global (fund)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4785,14 +4719,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEE ALSO open question 19 (2026-07-31): a candidate fee-drag switch to Valour Bitcoin Zero SEK (0% mgmt fee vs this certificate's 2.5-3.64%) is under evaluation - would preserve full BTC exposure (compatible with the hold decision below), not yet executed, spread/liquidity unverified. HOLD / SOFT-CAP DECISION 2026-07-22 (user-directed, REVERSES the earlier same-day trim): user will NOT sell any bitcoin for now. Total crypto (ETH 12,500 + COIN 16,503.12 = 29,003) stays at ~14.2% of the 203,754 SEK investable base, ABOVE the 10% high-risk-tier cap - user explicitly accepts the cap being breached for now ('if that means raising the crypto/high risk bar, then so be it for now'). Rationale: the active bullish BTC thesis (cycle position, mid-2028 halving) outweighs mechanical cap discipline at this time. SOFT-CAP mechanism instead of a sale: route this deployment and future monthly contributions to the secure/medium tiers so crypto DILUTES back toward 10% over time; revisit an actual trim only if crypto appreciates materially further (e.g. past ~15-16%). No tax event (nothing sold). Certificate-vs-self-custody (open Q13) remains SEPARATE; 'for now' answer is to KEEP the retained BTC in the ISK certificate - tax shelter beats the 2.5% fee at this size/horizon, and the user already holds direct/self-custody crypto via the ETH wallet. --- Original thesis (still held), user's own words: crypto is 'pretty low valued right now,' mid-2028 Bitcoin halving ahead, and there are 'positive buy-in signals now' - this is a cycle-position thesis for BTC exposure generally, not specific to the certificate structure. Separately, user has stated a structural preference for 'real bitcoin instead of certificates' going forward - see open_structural_questions for the certificate-vs-self-custody decision, not yet resolved. Factsheet CONFIRMED 2026-07-22: 2.5% annual management fee, tracks BTC ~1:1 before fees, no capital protection, high volatility/USD currency risk. Early redemption directly with the issuer incurs a 2% exit fee - does NOT apply to an ordinary exchange sale (broker fees apply instead). Live price CONFIRMED 2026-07-22 (user-reported from Avanza): market value 16,503.12 SEK (2,750.52/unit), up 36.39% (+4,403.12 SEK) since purchase (12,100 SEK cost basis for 6 units, consistent with the recorded 2,016.67/unit cost basis). Combined with the ETH wallet (12,500 SEK), total crypto exposure is now ~29,003.12 SEK - above both the 5% glidepath target and the 10% risk-tier cap; sizing decision pending, see open_structural_questions.</t>
+          <t>SETTLED 2026-07-29 (user-confirmed EXECUTED - this was previously recommended as the secure-tier deployment core but had NOT been logged as bought; user flagged the logging gap 2026-07-29). Global equity index fund, ~0.1% fee, the secure-tier core per the 60/30/10 risk-tier framework (investor_profile.json). Of this 119,999 SEK, ~59,050 SEK is earmarked 'medium-pending' per open question 16 - intended for gradual tax-free migration into individual quality stocks (Visa, Schneider, and a Swedish pick are the first migrations being evaluated 2026-07-29), NOT a permanent secure-tier allocation. Concentration note (flagged 2026-07-22, still applies): a global index fund alone is ~70% US mega-cap-tech weighted - paired with a distinct diversifier sleeve per the original deployment plan when remaining cash allows. Ticker/ISIN not yet recorded - TBD.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Avanza Global (fund)</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4807,14 +4741,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SETTLED 2026-07-29 (user-confirmed EXECUTED - this was previously recommended as the secure-tier deployment core but had NOT been logged as bought; user flagged the logging gap 2026-07-29). Global equity index fund, ~0.1% fee, the secure-tier core per the 60/30/10 risk-tier framework (investor_profile.json). Of this 119,999 SEK, ~59,050 SEK is earmarked 'medium-pending' per open question 16 - intended for gradual tax-free migration into individual quality stocks (Visa, Schneider, and a Swedish pick are the first migrations being evaluated 2026-07-29), NOT a permanent secure-tier allocation. Concentration note (flagged 2026-07-22, still applies): a global index fund alone is ~70% US mega-cap-tech weighted - paired with a distinct diversifier sleeve per the original deployment plan when remaining cash allows. Ticker/ISIN not yet recorded - TBD.</t>
+          <t>TBD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>SU.PA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4824,19 +4758,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>see thesis text</t>
+          <t>candidate — not held</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Western grid-buildout and energy-transition spending; data-center power demand.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Electrification + data-center power demand (the 'shovel' of the AI build-out) + energy-efficiency, all policy-funded. Quality compounder with pricing power; genuinely sustainability-aligned (its product IS efficiency, not a bolt-on label). Fits the user's Europe + sustainability + growth preference. Highest-conviction of this set.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SU.PA</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4856,19 +4800,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Western grid-buildout and energy-transition spending; data-center power demand.</t>
+          <t>US CHIPS Act + EU Chips Act reshoring subsidies drive fab build-out.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Electrification + data-center power demand (the 'shovel' of the AI build-out) + energy-efficiency, all policy-funded. Quality compounder with pricing power; genuinely sustainability-aligned (its product IS efficiency, not a bolt-on label). Fits the user's Europe + sustainability + growth preference. Highest-conviction of this set.</t>
+          <t>Effective monopoly on EUV lithography — no advanced chip exists without its machines. Wide moat, high margins, secular semiconductor demand.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4883,24 +4827,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>US CHIPS Act + EU Chips Act reshoring subsidies drive fab build-out.</t>
+          <t>EV adoption + electrification policy.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Effective monopoly on EUV lithography — no advanced chip exists without its machines. Wide moat, high margins, secular semiconductor demand.</t>
+          <t>European power-semiconductor leader levered to EV and industrial electrification — sustainability-adjacent growth.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>IBE.MC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4915,24 +4859,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EV adoption + electrification policy.</t>
+          <t>Renewable-energy subsidies and grid investment.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>European power-semiconductor leader levered to EV and industrial electrification — sustainability-adjacent growth.</t>
+          <t>Renewables-heavy regulated utility — a real sustainability holding and a steadier ballast within the medium tier.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IBE.MC</t>
+          <t>NOVO-B.CO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4947,24 +4891,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Renewable-energy subsidies and grid investment.</t>
+          <t>Drug-pricing politics run AGAINST this one (US pricing pressure) — a headwind, flagged honestly.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Renewables-heavy regulated utility — a real sustainability holding and a steadier ballast within the medium tier.</t>
+          <t>GLP-1 (obesity/diabetes) structural demand; dominant franchise, high margins.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOVO-B.CO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4984,42 +4928,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Drug-pricing politics run AGAINST this one (US pricing pressure) — a headwind, flagged honestly.</t>
+          <t>Reshoring subsidies (CHIPS Act) fund its US fabs.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>GLP-1 (obesity/diabetes) structural demand; dominant franchise, high margins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>candidate — not held</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Reshoring subsidies (CHIPS Act) fund its US fabs.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>The foundry essentially all advanced chips depend on; scale and process-node lead form a deep moat.</t>
         </is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -64,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,9 +96,10 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -485,14 +486,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-03 14:47 UTC from portfolio.json</t>
+          <t>Generated 2026-08-04 16:04 UTC from portfolio.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prices from snapshot: 20260803T135919.json</t>
+          <t>Prices from snapshot: 20260804T160037.json</t>
         </is>
       </c>
     </row>
@@ -545,16 +546,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>122164.65</v>
+        <v>146539.5</v>
       </c>
       <c r="C8" t="n">
-        <v>56.92</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>85</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-28.08</v>
+        <v>-16.57</v>
       </c>
     </row>
     <row r="9">
@@ -564,16 +565,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>52132.69</v>
+        <v>27253.8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.29</v>
+        <v>12.73</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>19.29</v>
+      <c r="E9" s="7" t="n">
+        <v>7.73</v>
       </c>
     </row>
     <row r="10">
@@ -586,13 +587,13 @@
         <v>24151</v>
       </c>
       <c r="C10" t="n">
-        <v>11.25</v>
+        <v>11.28</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>1.25</v>
+      <c r="E10" s="8" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="11">
@@ -605,7 +606,7 @@
         <v>16191</v>
       </c>
       <c r="C11" t="n">
-        <v>7.54</v>
+        <v>7.56</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -624,8 +625,8 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>214639.34</v>
+      <c r="B12" s="9" t="n">
+        <v>214135.3</v>
       </c>
     </row>
     <row r="13"/>
@@ -661,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -669,8 +670,8 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
@@ -759,7 +760,7 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>book</t>
         </is>
@@ -802,7 +803,7 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>book</t>
         </is>
@@ -833,10 +834,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>145.65</v>
+        <v>146.8</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.1268858800773695</v>
+        <v>0.1357833655705997</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -874,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2020</v>
+        <v>2047</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3920474123079042</v>
+        <v>0.4106539866308316</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -893,12 +894,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avanza Auto 3 (fund)</t>
+          <t>Volvo B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VOLV-B.ST</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -908,38 +909,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>16191</v>
+        <v>4802.2</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.6520922828892994</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>book</t>
+        <v>0.005170068027210846</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CoinShares XBT Provider Bitcoin Tracker One (certificate)</t>
+          <t>Atlas Copco B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COIN-XBT.ST</t>
+          <t>ATCO-B.ST</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -949,36 +950,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>crypto</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>15240</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.259502050409834</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>user-relayed</t>
+        <v>4781.7</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>-0.02289655172413797</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avanza Global (fund)</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>AZN.ST</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,35 +994,35 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="E8" t="n">
+        <v>4</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>119999</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>book</t>
+        <v>5896</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>-0.0218978102189781</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Avanza ISK available cash</t>
+          <t>Alfa Laval</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CASH_SEK</t>
+          <t>ALFA.ST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1029,45 +1032,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26400.3</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>26400.3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
+        <v>5101.2</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>-0.01323119777158767</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>book</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEB Osteuropafond (FROZEN - unsellable)</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>ABB.ST</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>seb-fund</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1075,89 +1076,81 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3765.6</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>-0.005871420123342125</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>no data</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Revolut everyday account (salary in, rent/food out)</t>
+          <t>Avanza Auto 3 (fund)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CASH_EUR</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>revolut</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>excluded_operating_cash</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1500</v>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>16564.8</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>live FX</t>
+        <v>16191</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.6520922828892994</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>book</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETH (self-custody wallet)</t>
+          <t>CoinShares XBT Provider Bitcoin Tracker One (certificate)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>COIN-XBT.ST</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eth-wallet</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1166,20 +1159,18 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.50185</v>
+        <v>6</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>8911</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
+        <v>15240</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.259502050409834</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>2.5</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>user-relayed</t>
         </is>
@@ -1188,84 +1179,299 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PayPal USD balance</t>
+          <t>Avanza Global (fund)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CASH_USD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>avanza-isk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1177.49</v>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>11421.417502</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>live FX</t>
+        <v>119999</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>book</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Avanza ISK available cash</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CASH_SEK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>avanza-isk</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1743.61</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1743.61</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SEB Osteuropafond (FROZEN - unsellable)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>seb-fund</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Revolut everyday account (salary in, rent/food out)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CASH_EUR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>revolut</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>excluded_operating_cash</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>16460.85</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>live FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ETH (self-custody wallet)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>eth-wallet</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>crypto</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.50185</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>8911</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>user-relayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PayPal USD balance</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CASH_USD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>paypal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1177.49</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11217.711732</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>no data</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>live FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>PayPal EUR balance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>CASH_EUR</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>paypal</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E19" t="n">
         <v>266.88</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>2947.209216</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F19" s="5" t="n">
+        <v>2928.714432</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>live FX</t>
         </is>
@@ -1293,22 +1499,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>total_value_sek</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>net_contribution_since_last_sek</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>note</t>
         </is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Value history" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Manual Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fundamentals" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="+0.0;-0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,7 +35,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
     <font>
       <i val="1"/>
@@ -42,10 +53,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005C6669"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,17 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,26 +96,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -466,14 +503,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,54 +521,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-04 16:04 UTC from portfolio.json</t>
+          <t>Generated 2026-08-04 17:02 UTC from portfolio.json</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Prices from snapshot: 20260804T160037.json</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Every number below is a live formula over the Holdings sheet - edit portfolio.json to change a fact, not this file.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>READ-ONLY VIEW — edit portfolio.json, not this file. Rebuild: python scripts/build_workbook.py</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Allocation vs target</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Exposure class</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Value (SEK)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>% of total</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Drift (pp)</t>
         </is>
@@ -542,58 +576,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>equity</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>146539.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>68.43000000000001</v>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <f>SUMIF(Holdings!$D$2:$D$19,"cash",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C8" s="7">
+        <f>IFERROR(B8/$B$12*100,"n/a")</f>
+        <v/>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>-16.57</v>
+        <v>5</v>
+      </c>
+      <c r="E8" s="8">
+        <f>IFERROR(C8-D8,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>27253.8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>12.73</v>
+          <t>crypto</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>SUMIF(Holdings!$D$2:$D$19,"crypto",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C9" s="7">
+        <f>IFERROR(B9/$B$12*100,"n/a")</f>
+        <v/>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>7.73</v>
+        <v>10</v>
+      </c>
+      <c r="E9" s="8">
+        <f>IFERROR(C9-D9,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>crypto</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>24151</v>
-      </c>
-      <c r="C10" t="n">
-        <v>11.28</v>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <f>SUMIF(Holdings!$D$2:$D$19,"equity",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>IFERROR(B10/$B$12*100,"n/a")</f>
+        <v/>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1.28</v>
+        <v>85</v>
+      </c>
+      <c r="E10" s="8">
+        <f>IFERROR(C10-D10,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -602,11 +645,13 @@
           <t>mixed</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>16191</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7.56</v>
+      <c r="B11" s="6">
+        <f>SUMIF(Holdings!$D$2:$D$19,"mixed",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>IFERROR(B11/$B$12*100,"n/a")</f>
+        <v/>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -620,38 +665,180 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>214135.3</v>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="B12" s="9">
+        <f>SUMIF(Holdings!$D$2:$D$19,"&lt;&gt;excluded_operating_cash",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Cross-check</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>BY TYPE</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>If this total does not match your broker, the system's model is wrong — that mismatch is the point of this sheet.</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Instrument type</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Value (SEK)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>SUMIF(Holdings!$E$2:$E$19,"cash",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(Holdings!$E$2:$E$19,"cash")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>certificate</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>SUMIF(Holdings!$E$2:$E$19,"certificate",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>COUNTIF(Holdings!$E$2:$E$19,"certificate")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>SUMIF(Holdings!$E$2:$E$19,"fund",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(Holdings!$E$2:$E$19,"fund")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>spot_crypto</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>SUMIF(Holdings!$E$2:$E$19,"spot_crypto",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(Holdings!$E$2:$E$19,"spot_crypto")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>SUMIF(Holdings!$E$2:$E$19,"stock",Holdings!$G$2:$G$19)</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>COUNTIF(Holdings!$E$2:$E$19,"stock")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>FEE DRAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Total annual fees (SEK/yr)</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>SUMPRODUCT((Holdings!$I$2:$I$19&lt;&gt;"")*IFERROR(Holdings!$I$2:$I$19/100,0)*IFERROR(Holdings!$G$2:$G$19,0))</f>
+        <v/>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Sum of fee%/yr x value per holding, over Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>If TOTAL above does not match your broker, the system's model is wrong — that mismatch is the point of this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Deliberately excluded (operating cash, not capital): Revolut everyday account (salary in, rent/food out)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E8:E11">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="0">
+      <formula>-10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="1">
+      <formula>3</formula>
+      <formula>9.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="1">
+      <formula>-9.99</formula>
+      <formula>-3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="between" dxfId="2">
+      <formula>-2.99</formula>
+      <formula>2.99</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -662,78 +849,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Exposure class</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Instrument type</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Value (SEK)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Cost basis (SEK)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Fee %/yr</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Price source</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>Δ vs cost</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Fee %/yr</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Price source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CASH_SEK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Tax-reserve sparkonto (2027 deklaration - confirmed HB + SEB capital-gains tax)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CASH_SEK</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>hb-main</t>
@@ -744,39 +943,48 @@
           <t>cash</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>10752.76</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>10752.76</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>book</t>
         </is>
+      </c>
+      <c r="K2" s="14">
+        <f>IFERROR((G2-H2)/H2,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CASH_SEK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Handelsbanken normal/checking account</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CASH_SEK</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>hb-checking</t>
@@ -787,39 +995,48 @@
           <t>cash</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>611</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>611</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>book</t>
         </is>
+      </c>
+      <c r="K3" s="14">
+        <f>IFERROR((G3-H3)/H3,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>SHB-A.ST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Handelsbanken A (stock)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SHB-A.ST</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -830,37 +1047,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>146.8</v>
       </c>
-      <c r="G4" s="10" t="n">
-        <v>0.1357833655705997</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="6" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K4" s="14">
+        <f>IFERROR((G4-H4)/H4,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>INVE-A.ST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Investor A (stock)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>INVE-A.ST</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -871,37 +1097,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>2047</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>0.4106539866308316</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="6" t="n">
+        <v>1451.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K5" s="14">
+        <f>IFERROR((G5-H5)/H5,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>VOLV-B.ST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Volvo B</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VOLV-B.ST</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -912,37 +1147,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>13</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>4802.2</v>
       </c>
-      <c r="G6" s="10" t="n">
-        <v>0.005170068027210846</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="6" t="n">
+        <v>4777.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K6" s="14">
+        <f>IFERROR((G6-H6)/H6,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>ATCO-B.ST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Atlas Copco B</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ATCO-B.ST</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -953,37 +1197,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>27</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>4781.7</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>-0.02289655172413797</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="6" t="n">
+        <v>4893.75</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K7" s="14">
+        <f>IFERROR((G7-H7)/H7,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>AZN.ST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>AstraZeneca</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AZN.ST</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -994,37 +1247,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>5896</v>
       </c>
-      <c r="G8" s="11" t="n">
-        <v>-0.0218978102189781</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="6" t="n">
+        <v>6028</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K8" s="14">
+        <f>IFERROR((G8-H8)/H8,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ALFA.ST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Alfa Laval</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ALFA.ST</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -1035,37 +1297,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>5101.2</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>-0.01323119777158767</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="6" t="n">
+        <v>5169.599999999999</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K9" s="14">
+        <f>IFERROR((G9-H9)/H9,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ABB.ST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ABB.ST</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -1076,37 +1347,46 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>3765.6</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <v>-0.005871420123342125</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="6" t="n">
+        <v>3787.84</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>live</t>
         </is>
+      </c>
+      <c r="K10" s="14">
+        <f>IFERROR((G10-H10)/H10,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Avanza Auto 3 (fund)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -1119,35 +1399,44 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>16191</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>0.6520922828892994</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="H11" s="6" t="n">
+        <v>9800.299999999999</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.39</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>book</t>
         </is>
+      </c>
+      <c r="K11" s="14">
+        <f>IFERROR((G11-H11)/H11,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>COIN-XBT.ST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>CoinShares XBT Provider Bitcoin Tracker One (certificate)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>COIN-XBT.ST</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -1158,35 +1447,44 @@
           <t>crypto</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>certificate</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>15240</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>0.259502050409834</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="H12" s="6" t="n">
+        <v>12100.02</v>
+      </c>
+      <c r="I12" t="n">
         <v>2.5</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>user-relayed</t>
         </is>
+      </c>
+      <c r="K12" s="14">
+        <f>IFERROR((G12-H12)/H12,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Avanza Global (fund)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -1199,35 +1497,44 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <v>119999</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="H13" s="6" t="n">
+        <v>119999</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>book</t>
         </is>
+      </c>
+      <c r="K13" s="14">
+        <f>IFERROR((G13-H13)/H13,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>CASH_SEK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Avanza ISK available cash</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CASH_SEK</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>avanza-isk</t>
@@ -1238,39 +1545,48 @@
           <t>cash</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>1743.61</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <v>1743.61</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>book</t>
         </is>
+      </c>
+      <c r="K14" s="14">
+        <f>IFERROR((G14-H14)/H14,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>SEB Osteuropafond (FROZEN - unsellable)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>seb-fund</t>
@@ -1283,41 +1599,48 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>no data</t>
-        </is>
+      <c r="K15" s="14">
+        <f>IFERROR((G15-H15)/H15,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CASH_EUR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Revolut everyday account (salary in, rent/food out)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CASH_EUR</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>revolut</t>
@@ -1328,39 +1651,48 @@
           <t>excluded_operating_cash</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>1500</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <v>16460.85</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>live FX</t>
         </is>
+      </c>
+      <c r="K16" s="14">
+        <f>IFERROR((G16-H16)/H16,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>ETH (self-custody wallet)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>eth-wallet</t>
@@ -1371,37 +1703,46 @@
           <t>crypto</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>spot_crypto</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>0.50185</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>8911</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>user-relayed</t>
         </is>
+      </c>
+      <c r="K17" s="14">
+        <f>IFERROR((G17-H17)/H17,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>CASH_USD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>PayPal USD balance</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CASH_USD</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>paypal</t>
@@ -1412,39 +1753,48 @@
           <t>cash</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>1177.49</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="6" t="n">
         <v>11217.711732</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>live FX</t>
         </is>
+      </c>
+      <c r="K18" s="14">
+        <f>IFERROR((G18-H18)/H18,"no data")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>CASH_EUR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>PayPal EUR balance</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CASH_EUR</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>paypal</t>
@@ -1455,26 +1805,35 @@
           <t>cash</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>266.88</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>2928.714432</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>no data</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>live FX</t>
         </is>
+      </c>
+      <c r="K19" s="14">
+        <f>IFERROR((G19-H19)/H19,"no data")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1750,4 +2109,203 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>week52_high</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>week52_low</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Use Excel's Stocks data type on the ticker, pull whatever fields you want into this row's columns, save. This sheet survives rebuilds. Run scripts/import_fundamentals_tab.py to fold values into data/company_profiles/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ABB.ST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALFA.ST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alfa Laval</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ATCO-B.ST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Atlas Copco B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AZN.ST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COIN-XBT.ST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CoinShares XBT Provider Bitcoin Tracker One (certificate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INVE-A.ST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Investor A (stock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SHB-A.ST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Handelsbanken A (stock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VOLV-B.ST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Volvo B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>